--- a/Mataquito/supplemental/Table_S2.xlsx
+++ b/Mataquito/supplemental/Table_S2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/Chapter_1_Manuscript/MataquitoWatershedAnalysis/Mataquito/data/sample_metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/Chapter_1_Manuscript/MataquitoWatershedAnalysis/Mataquito/supplemental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F60479A-C63E-8C48-9832-304917FD44DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F948FC-AFD2-5345-8ADC-8B7F986F01C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,6 +115,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -495,10 +496,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -702,7 +699,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
@@ -711,7 +708,7 @@
     <col min="5" max="5" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -728,14 +725,8 @@
         <v>4</v>
       </c>
       <c r="F1" s="10"/>
-      <c r="G1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -751,240 +742,270 @@
       <c r="E2" s="3">
         <v>6.9972365267044867E-2</v>
       </c>
-      <c r="G2" s="4">
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>36.130859999999998</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1599.7308599999999</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2.2585586677999075E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>145.1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>50.50488</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1057.4048799999998</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.18498579276464094</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
+        <v>35.28481</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1447.2848100000001</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.438000437522729E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>17.613589999999999</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1210.2135899999998</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.4554116848084643E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>17.24784</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1346.24784</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.2811786572671492E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6.4854099999999999</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1136.1854100000003</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5.7080560469439561E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <v>9.4085999999999999</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2566.5086000000006</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.665914074864194E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2">
+        <v>23.845870000000001</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4147.3458700000001</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.7496699690493865E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2">
+        <v>10.72424</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3257.72424</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.2919422301993248E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>9.5632000000000001</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2455.6632</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.8943451202917406E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B15" s="4">
         <f>E6/E7</f>
         <v>1.1359943256571001</v>
       </c>
-      <c r="H2" s="5">
-        <v>46148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>36.130859999999998</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1599.7308599999999</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2.2585586677999075E-2</v>
-      </c>
-      <c r="G3" s="4">
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="4">
         <f>E4/E9</f>
         <v>50.461027996542406</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1">
-        <v>145.1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>50.50488</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1057.4048799999998</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.18498579276464094</v>
-      </c>
-      <c r="G4" s="4">
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="5">
+        <v>46092</v>
+      </c>
+      <c r="B17" s="4">
         <f>E4/E12</f>
         <v>47.501129728015201</v>
       </c>
-      <c r="H4" s="5">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
-        <v>35.28481</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1447.2848100000001</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2.438000437522729E-2</v>
-      </c>
-      <c r="G5" s="4">
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B18" s="4">
         <f>E4/E11</f>
         <v>56.193511255341861</v>
       </c>
-      <c r="H5" s="5">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2">
-        <v>17.613589999999999</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1210.2135899999998</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1.4554116848084643E-2</v>
-      </c>
-      <c r="G6" s="4">
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5">
+        <v>46085</v>
+      </c>
+      <c r="B19" s="4">
         <f>E4/E5</f>
         <v>7.5876029354861982</v>
       </c>
-      <c r="H6" s="5">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2">
-        <v>17.24784</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1346.24784</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1.2811786572671492E-2</v>
-      </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2">
-        <v>6.4854099999999999</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1136.1854100000003</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5.7080560469439561E-3</v>
-      </c>
-      <c r="G8" s="4">
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5">
+        <v>46087</v>
+      </c>
+      <c r="B21" s="4">
         <f>E4/E7</f>
         <v>14.438719511549591</v>
       </c>
-      <c r="H8" s="5">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2">
-        <v>9.4085999999999999</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2566.5086000000006</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3.665914074864194E-3</v>
-      </c>
-      <c r="G9" s="4">
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5">
+        <v>46086</v>
+      </c>
+      <c r="B22" s="4">
         <f>E4/E6</f>
         <v>12.710203902821181</v>
       </c>
-      <c r="H9" s="5">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2">
-        <v>23.845870000000001</v>
-      </c>
-      <c r="D10" s="2">
-        <v>4147.3458700000001</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5.7496699690493865E-3</v>
-      </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2">
-        <v>10.72424</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3257.72424</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.2919422301993248E-3</v>
-      </c>
-      <c r="G11" s="4">
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="5">
+        <v>46090</v>
+      </c>
+      <c r="B24" s="4">
         <f>E4/E10</f>
         <v>32.173288860130057</v>
       </c>
-      <c r="H11" s="5">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2">
-        <v>9.5632000000000001</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2455.6632</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3.8943451202917406E-3</v>
-      </c>
-      <c r="G12" s="4">
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B25" s="4">
         <f>E4/E3</f>
         <v>8.1904355818588552</v>
-      </c>
-      <c r="H12" s="5">
-        <v>46083</v>
       </c>
     </row>
   </sheetData>

--- a/Mataquito/supplemental/Table_S2.xlsx
+++ b/Mataquito/supplemental/Table_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/Chapter_1_Manuscript/MataquitoWatershedAnalysis/Mataquito/supplemental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F948FC-AFD2-5345-8ADC-8B7F986F01C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96802C7F-C237-DF4C-A84B-9703F6A9EAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>Sample ID</t>
   </si>
@@ -65,9 +65,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>3/8.2</t>
-  </si>
-  <si>
     <t>CT-3</t>
   </si>
   <si>
@@ -93,6 +90,33 @@
   </si>
   <si>
     <t>CT-11</t>
+  </si>
+  <si>
+    <t>CT-5/CT-6</t>
+  </si>
+  <si>
+    <t>CT-3/CT-8.2</t>
+  </si>
+  <si>
+    <t>CT-3/CT-11</t>
+  </si>
+  <si>
+    <t>CT-3/CT-10</t>
+  </si>
+  <si>
+    <t>CT-3/CT-4</t>
+  </si>
+  <si>
+    <t>CT-3/CT-6</t>
+  </si>
+  <si>
+    <t>CT-3/CT-5</t>
+  </si>
+  <si>
+    <t>CT-3/CT-9</t>
+  </si>
+  <si>
+    <t>CT-3/CT-2</t>
   </si>
 </sst>
 </file>
@@ -104,7 +128,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="m/d"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -121,6 +145,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -162,9 +193,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -174,6 +202,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,22 +738,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10"/>
+      <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -762,7 +791,7 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>145.1</v>
@@ -779,7 +808,7 @@
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>9</v>
@@ -796,7 +825,7 @@
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>9</v>
@@ -813,7 +842,7 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>9</v>
@@ -830,7 +859,7 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>9</v>
@@ -847,7 +876,7 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
@@ -864,7 +893,7 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
@@ -881,7 +910,7 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
@@ -898,7 +927,7 @@
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
@@ -914,16 +943,16 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="5">
-        <v>46148</v>
+      <c r="A15" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B15" s="4">
         <f>E6/E7</f>
@@ -931,8 +960,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="7" t="s">
-        <v>10</v>
+      <c r="A16" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="B16" s="4">
         <f>E4/E9</f>
@@ -940,8 +969,8 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="5">
-        <v>46092</v>
+      <c r="A17" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="B17" s="4">
         <f>E4/E12</f>
@@ -949,8 +978,8 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="5">
-        <v>46091</v>
+      <c r="A18" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="B18" s="4">
         <f>E4/E11</f>
@@ -958,8 +987,8 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="5">
-        <v>46085</v>
+      <c r="A19" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="B19" s="4">
         <f>E4/E5</f>
@@ -970,8 +999,8 @@
       <c r="B20" s="4"/>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="5">
-        <v>46087</v>
+      <c r="A21" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="B21" s="4">
         <f>E4/E7</f>
@@ -979,8 +1008,8 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="5">
-        <v>46086</v>
+      <c r="A22" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B22" s="4">
         <f>E4/E6</f>
@@ -991,8 +1020,8 @@
       <c r="B23" s="4"/>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="5">
-        <v>46090</v>
+      <c r="A24" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="B24" s="4">
         <f>E4/E10</f>
@@ -1000,8 +1029,8 @@
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="5">
-        <v>46083</v>
+      <c r="A25" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="B25" s="4">
         <f>E4/E3</f>
